--- a/salidas/empresas/V.xlsx
+++ b/salidas/empresas/V.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Acciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +22,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -432,48 +444,48 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B2" t="n">
-        <v>13.67852306365967</v>
+        <v>13.6785249710083</v>
       </c>
       <c r="C2" t="n">
         <v>15.59000015258789</v>
@@ -486,11 +498,11 @@
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B3" t="n">
-        <v>18.30457305908203</v>
+        <v>18.3045654296875</v>
       </c>
       <c r="C3" t="n">
         <v>20.86249923706055</v>
@@ -503,11 +515,11 @@
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B4" t="n">
-        <v>18.94287490844727</v>
+        <v>18.94286727905273</v>
       </c>
       <c r="C4" t="n">
         <v>21.59000015258789</v>
@@ -520,7 +532,7 @@
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B5" t="n">
@@ -537,11 +549,11 @@
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B6" t="n">
-        <v>16.02554512023926</v>
+        <v>16.02555465698242</v>
       </c>
       <c r="C6" t="n">
         <v>18.26499938964844</v>
@@ -554,11 +566,11 @@
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B7" t="n">
-        <v>16.67253684997559</v>
+        <v>16.67253875732422</v>
       </c>
       <c r="C7" t="n">
         <v>18.97500038146973</v>
@@ -571,11 +583,11 @@
       <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B8" t="n">
-        <v>13.48521137237549</v>
+        <v>13.48520851135254</v>
       </c>
       <c r="C8" t="n">
         <v>15.34749984741211</v>
@@ -588,11 +600,11 @@
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B9" t="n">
-        <v>12.1584300994873</v>
+        <v>12.15843486785889</v>
       </c>
       <c r="C9" t="n">
         <v>13.83749961853027</v>
@@ -605,11 +617,11 @@
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B10" t="n">
-        <v>11.56815147399902</v>
+        <v>11.56815242767334</v>
       </c>
       <c r="C10" t="n">
         <v>13.14000034332275</v>
@@ -622,11 +634,11 @@
       <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B11" t="n">
-        <v>11.5439453125</v>
+        <v>11.54394435882568</v>
       </c>
       <c r="C11" t="n">
         <v>13.11250019073486</v>
@@ -639,7 +651,7 @@
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B12" t="n">
@@ -656,11 +668,11 @@
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B13" t="n">
-        <v>12.50592994689941</v>
+        <v>12.50592708587646</v>
       </c>
       <c r="C13" t="n">
         <v>14.17749977111816</v>
@@ -673,11 +685,11 @@
       <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B14" t="n">
-        <v>12.26114654541016</v>
+        <v>12.26114940643311</v>
       </c>
       <c r="C14" t="n">
         <v>13.89999961853027</v>
@@ -690,11 +702,11 @@
       <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B15" t="n">
-        <v>14.32525730133057</v>
+        <v>14.32525062561035</v>
       </c>
       <c r="C15" t="n">
         <v>16.23999977111816</v>
@@ -707,11 +719,11 @@
       <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B16" t="n">
-        <v>14.95577049255371</v>
+        <v>14.95577239990234</v>
       </c>
       <c r="C16" t="n">
         <v>16.92749977111816</v>
@@ -724,11 +736,11 @@
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B17" t="n">
-        <v>13.75197887420654</v>
+        <v>13.75197410583496</v>
       </c>
       <c r="C17" t="n">
         <v>15.5649995803833</v>
@@ -741,11 +753,11 @@
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B18" t="n">
-        <v>14.45879554748535</v>
+        <v>14.4587926864624</v>
       </c>
       <c r="C18" t="n">
         <v>16.36499977111816</v>
@@ -758,11 +770,11 @@
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B19" t="n">
-        <v>15.72862720489502</v>
+        <v>15.72862529754639</v>
       </c>
       <c r="C19" t="n">
         <v>17.77499961853027</v>
@@ -775,11 +787,11 @@
       <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B20" t="n">
-        <v>15.2883996963501</v>
+        <v>15.28840732574463</v>
       </c>
       <c r="C20" t="n">
         <v>17.27750015258789</v>
@@ -792,11 +804,11 @@
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B21" t="n">
-        <v>16.75950241088867</v>
+        <v>16.75950622558594</v>
       </c>
       <c r="C21" t="n">
         <v>18.94000053405762</v>
@@ -809,11 +821,11 @@
       <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B22" t="n">
-        <v>17.94644355773926</v>
+        <v>17.94643974304199</v>
       </c>
       <c r="C22" t="n">
         <v>20.25</v>
@@ -832,11 +844,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B23" t="n">
-        <v>19.37772178649902</v>
+        <v>19.37772750854492</v>
       </c>
       <c r="C23" t="n">
         <v>21.86499977111816</v>
@@ -855,11 +867,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B24" t="n">
-        <v>18.17463874816895</v>
+        <v>18.17464828491211</v>
       </c>
       <c r="C24" t="n">
         <v>20.50749969482422</v>
@@ -878,11 +890,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B25" t="n">
-        <v>18.92312812805176</v>
+        <v>18.92313194274902</v>
       </c>
       <c r="C25" t="n">
         <v>21.31999969482422</v>
@@ -901,11 +913,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B26" t="n">
-        <v>20.19902610778809</v>
+        <v>20.19902420043945</v>
       </c>
       <c r="C26" t="n">
         <v>22.75749969482422</v>
@@ -924,11 +936,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B27" t="n">
-        <v>20.02150344848633</v>
+        <v>20.02150535583496</v>
       </c>
       <c r="C27" t="n">
         <v>22.5575008392334</v>
@@ -947,11 +959,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B28" t="n">
-        <v>16.10235977172852</v>
+        <v>16.10237503051758</v>
       </c>
       <c r="C28" t="n">
         <v>18.11499977111816</v>
@@ -970,11 +982,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B29" t="n">
-        <v>15.72236156463623</v>
+        <v>15.7223596572876</v>
       </c>
       <c r="C29" t="n">
         <v>17.6875</v>
@@ -993,11 +1005,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B30" t="n">
-        <v>16.30014991760254</v>
+        <v>16.30014419555664</v>
       </c>
       <c r="C30" t="n">
         <v>18.33749961853027</v>
@@ -1016,11 +1028,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B31" t="n">
-        <v>15.35452270507812</v>
+        <v>15.35452842712402</v>
       </c>
       <c r="C31" t="n">
         <v>17.2450008392334</v>
@@ -1039,11 +1051,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B32" t="n">
-        <v>16.52981758117676</v>
+        <v>16.52982139587402</v>
       </c>
       <c r="C32" t="n">
         <v>18.56500053405762</v>
@@ -1056,11 +1068,11 @@
       <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B33" t="n">
-        <v>17.3979377746582</v>
+        <v>17.3979320526123</v>
       </c>
       <c r="C33" t="n">
         <v>19.54000091552734</v>
@@ -1073,11 +1085,11 @@
       <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B34" t="n">
-        <v>16.47150802612305</v>
+        <v>16.47150230407715</v>
       </c>
       <c r="C34" t="n">
         <v>18.46249961853027</v>
@@ -1090,11 +1102,11 @@
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B35" t="n">
-        <v>15.69755077362061</v>
+        <v>15.69755554199219</v>
       </c>
       <c r="C35" t="n">
         <v>17.59499931335449</v>
@@ -1107,11 +1119,11 @@
       <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B36" t="n">
-        <v>15.57933902740479</v>
+        <v>15.57934761047363</v>
       </c>
       <c r="C36" t="n">
         <v>17.46249961853027</v>
@@ -1124,11 +1136,11 @@
       <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B37" t="n">
-        <v>16.32591819763184</v>
+        <v>16.32590866088867</v>
       </c>
       <c r="C37" t="n">
         <v>18.26250076293945</v>
@@ -1141,11 +1153,11 @@
       <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B38" t="n">
-        <v>16.45329666137695</v>
+        <v>16.45330238342285</v>
       </c>
       <c r="C38" t="n">
         <v>18.40500068664551</v>
@@ -1158,11 +1170,11 @@
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B39" t="n">
-        <v>17.45900726318359</v>
+        <v>17.4590015411377</v>
       </c>
       <c r="C39" t="n">
         <v>19.53000068664551</v>
@@ -1175,11 +1187,11 @@
       <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B40" t="n">
-        <v>18.14984321594238</v>
+        <v>18.14983940124512</v>
       </c>
       <c r="C40" t="n">
         <v>20.26499938964844</v>
@@ -1192,11 +1204,11 @@
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B41" t="n">
-        <v>18.86634254455566</v>
+        <v>18.8663387298584</v>
       </c>
       <c r="C41" t="n">
         <v>21.06500053405762</v>
@@ -1209,11 +1221,11 @@
       <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B42" t="n">
-        <v>19.15294075012207</v>
+        <v>19.15294456481934</v>
       </c>
       <c r="C42" t="n">
         <v>21.38500022888184</v>
@@ -1226,11 +1238,11 @@
       <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B43" t="n">
-        <v>19.71132659912109</v>
+        <v>19.71133995056152</v>
       </c>
       <c r="C43" t="n">
         <v>21.96999931335449</v>
@@ -1243,11 +1255,11 @@
       <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B44" t="n">
-        <v>19.22684097290039</v>
+        <v>19.22685050964355</v>
       </c>
       <c r="C44" t="n">
         <v>21.43000030517578</v>
@@ -1260,11 +1272,11 @@
       <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B45" t="n">
-        <v>20.91805458068848</v>
+        <v>20.91806602478027</v>
       </c>
       <c r="C45" t="n">
         <v>23.31500053405762</v>
@@ -1277,11 +1289,11 @@
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B46" t="n">
-        <v>21.80036163330078</v>
+        <v>21.80035972595215</v>
       </c>
       <c r="C46" t="n">
         <v>24.24250030517578</v>
@@ -1294,11 +1306,11 @@
       <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B47" t="n">
-        <v>22.82551574707031</v>
+        <v>22.82551383972168</v>
       </c>
       <c r="C47" t="n">
         <v>25.38249969482422</v>
@@ -1311,11 +1323,11 @@
       <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B48" t="n">
-        <v>22.62542724609375</v>
+        <v>22.62542533874512</v>
       </c>
       <c r="C48" t="n">
         <v>25.15999984741211</v>
@@ -1328,11 +1340,11 @@
       <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B49" t="n">
-        <v>26.21181678771973</v>
+        <v>26.21181297302246</v>
       </c>
       <c r="C49" t="n">
         <v>29.09250068664551</v>
@@ -1345,11 +1357,11 @@
       <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B50" t="n">
-        <v>26.57896041870117</v>
+        <v>26.57897186279297</v>
       </c>
       <c r="C50" t="n">
         <v>29.5</v>
@@ -1362,11 +1374,11 @@
       <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B51" t="n">
-        <v>27.70069122314453</v>
+        <v>27.7006893157959</v>
       </c>
       <c r="C51" t="n">
         <v>30.7450008392334</v>
@@ -1379,11 +1391,11 @@
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B52" t="n">
-        <v>25.99732208251953</v>
+        <v>25.9973258972168</v>
       </c>
       <c r="C52" t="n">
         <v>28.79999923706055</v>
@@ -1396,7 +1408,7 @@
       <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B53" t="n">
@@ -1413,11 +1425,11 @@
       <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B54" t="n">
-        <v>29.12738227844238</v>
+        <v>29.12738037109375</v>
       </c>
       <c r="C54" t="n">
         <v>32.26750183105469</v>
@@ -1430,11 +1442,11 @@
       <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B55" t="n">
-        <v>28.99143600463867</v>
+        <v>28.99144172668457</v>
       </c>
       <c r="C55" t="n">
         <v>32.0625</v>
@@ -1447,11 +1459,11 @@
       <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B56" t="n">
-        <v>30.35454177856445</v>
+        <v>30.35453033447266</v>
       </c>
       <c r="C56" t="n">
         <v>33.56999969482422</v>
@@ -1464,11 +1476,11 @@
       <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B57" t="n">
-        <v>31.36726188659668</v>
+        <v>31.36726760864258</v>
       </c>
       <c r="C57" t="n">
         <v>34.68999862670898</v>
@@ -1481,11 +1493,11 @@
       <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B58" t="n">
-        <v>33.9211311340332</v>
+        <v>33.92113876342773</v>
       </c>
       <c r="C58" t="n">
         <v>37.4275016784668</v>
@@ -1498,11 +1510,11 @@
       <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B59" t="n">
-        <v>34.3448486328125</v>
+        <v>34.34484100341797</v>
       </c>
       <c r="C59" t="n">
         <v>37.89500045776367</v>
@@ -1515,7 +1527,7 @@
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B60" t="n">
@@ -1532,11 +1544,11 @@
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B61" t="n">
-        <v>36.02028656005859</v>
+        <v>36.02029418945312</v>
       </c>
       <c r="C61" t="n">
         <v>39.65999984741211</v>
@@ -1549,11 +1561,11 @@
       <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B62" t="n">
-        <v>38.56333541870117</v>
+        <v>38.56333923339844</v>
       </c>
       <c r="C62" t="n">
         <v>42.45999908447266</v>
@@ -1566,11 +1578,11 @@
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B63" t="n">
-        <v>38.25</v>
+        <v>38.2499885559082</v>
       </c>
       <c r="C63" t="n">
         <v>42.1150016784668</v>
@@ -1583,11 +1595,11 @@
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B64" t="n">
-        <v>40.52206802368164</v>
+        <v>40.52207183837891</v>
       </c>
       <c r="C64" t="n">
         <v>44.53499984741211</v>
@@ -1600,11 +1612,11 @@
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B65" t="n">
-        <v>41.57072448730469</v>
+        <v>41.57071685791016</v>
       </c>
       <c r="C65" t="n">
         <v>45.6875</v>
@@ -1617,11 +1629,11 @@
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B66" t="n">
-        <v>40.26502990722656</v>
+        <v>40.26501846313477</v>
       </c>
       <c r="C66" t="n">
         <v>44.25249862670898</v>
@@ -1634,11 +1646,11 @@
       <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B67" t="n">
-        <v>39.74903869628906</v>
+        <v>39.74906158447266</v>
       </c>
       <c r="C67" t="n">
         <v>43.60499954223633</v>
@@ -1651,11 +1663,11 @@
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B68" t="n">
-        <v>43.5503044128418</v>
+        <v>43.55029296875</v>
       </c>
       <c r="C68" t="n">
         <v>47.77500152587891</v>
@@ -1668,11 +1680,11 @@
       <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B69" t="n">
-        <v>44.81966400146484</v>
+        <v>44.81966018676758</v>
       </c>
       <c r="C69" t="n">
         <v>49.16749954223633</v>
@@ -1685,11 +1697,11 @@
       <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B70" t="n">
-        <v>46.46078109741211</v>
+        <v>46.46078872680664</v>
       </c>
       <c r="C70" t="n">
         <v>50.8650016784668</v>
@@ -1702,11 +1714,11 @@
       <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B71" t="n">
-        <v>50.84972763061523</v>
+        <v>50.8497428894043</v>
       </c>
       <c r="C71" t="n">
         <v>55.66999816894531</v>
@@ -1719,11 +1731,11 @@
       <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B72" t="n">
-        <v>49.19417953491211</v>
+        <v>49.19418334960938</v>
       </c>
       <c r="C72" t="n">
         <v>53.85749816894531</v>
@@ -1736,11 +1748,11 @@
       <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B73" t="n">
-        <v>51.68716430664062</v>
+        <v>51.68717193603516</v>
       </c>
       <c r="C73" t="n">
         <v>56.48500061035156</v>
@@ -1753,11 +1765,11 @@
       <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B74" t="n">
-        <v>49.38121795654297</v>
+        <v>49.38122177124023</v>
       </c>
       <c r="C74" t="n">
         <v>53.96500015258789</v>
@@ -1770,11 +1782,11 @@
       <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B75" t="n">
-        <v>46.35007858276367</v>
+        <v>46.35008239746094</v>
       </c>
       <c r="C75" t="n">
         <v>50.65250015258789</v>
@@ -1787,11 +1799,11 @@
       <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B76" t="n">
-        <v>49.23846054077148</v>
+        <v>49.23847198486328</v>
       </c>
       <c r="C76" t="n">
         <v>53.70750045776367</v>
@@ -1804,11 +1816,11 @@
       <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B77" t="n">
-        <v>48.2941780090332</v>
+        <v>48.29418182373047</v>
       </c>
       <c r="C77" t="n">
         <v>52.6775016784668</v>
@@ -1821,11 +1833,11 @@
       <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B78" t="n">
-        <v>48.36293029785156</v>
+        <v>48.36294174194336</v>
       </c>
       <c r="C78" t="n">
         <v>52.75249862670898</v>
@@ -1838,11 +1850,11 @@
       <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B79" t="n">
-        <v>48.80184936523438</v>
+        <v>48.80183410644531</v>
       </c>
       <c r="C79" t="n">
         <v>53.13000106811523</v>
@@ -1855,11 +1867,11 @@
       <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B80" t="n">
-        <v>48.99702835083008</v>
+        <v>48.99703216552734</v>
       </c>
       <c r="C80" t="n">
         <v>53.34249877929688</v>
@@ -1872,7 +1884,7 @@
       <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B81" t="n">
@@ -1889,7 +1901,7 @@
       <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B82" t="n">
@@ -1906,11 +1918,11 @@
       <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B83" t="n">
-        <v>60.32601547241211</v>
+        <v>60.32600402832031</v>
       </c>
       <c r="C83" t="n">
         <v>65.55000305175781</v>
@@ -1923,11 +1935,11 @@
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B84" t="n">
-        <v>58.64874649047852</v>
+        <v>58.64876174926758</v>
       </c>
       <c r="C84" t="n">
         <v>63.72750091552734</v>
@@ -1940,11 +1952,11 @@
       <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B85" t="n">
-        <v>62.53545379638672</v>
+        <v>62.53546142578125</v>
       </c>
       <c r="C85" t="n">
         <v>67.82749938964844</v>
@@ -1957,11 +1969,11 @@
       <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B86" t="n">
-        <v>60.30660629272461</v>
+        <v>60.30658721923828</v>
       </c>
       <c r="C86" t="n">
         <v>65.41000366210938</v>
@@ -1974,11 +1986,11 @@
       <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B87" t="n">
-        <v>60.89667129516602</v>
+        <v>60.89664840698242</v>
       </c>
       <c r="C87" t="n">
         <v>66.05000305175781</v>
@@ -1991,11 +2003,11 @@
       <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B88" t="n">
-        <v>63.43228912353516</v>
+        <v>63.43225479125977</v>
       </c>
       <c r="C88" t="n">
         <v>68.68000030517578</v>
@@ -2008,11 +2020,11 @@
       <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B89" t="n">
-        <v>62.01920318603516</v>
+        <v>62.01919174194336</v>
       </c>
       <c r="C89" t="n">
         <v>67.15000152587891</v>
@@ -2025,11 +2037,11 @@
       <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B90" t="n">
-        <v>69.58338928222656</v>
+        <v>69.58338165283203</v>
       </c>
       <c r="C90" t="n">
         <v>75.33999633789062</v>
@@ -2042,11 +2054,11 @@
       <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B91" t="n">
-        <v>65.96000671386719</v>
+        <v>65.95998382568359</v>
       </c>
       <c r="C91" t="n">
         <v>71.30000305175781</v>
@@ -2059,11 +2071,11 @@
       <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B92" t="n">
-        <v>64.44279479980469</v>
+        <v>64.44281005859375</v>
       </c>
       <c r="C92" t="n">
         <v>69.66000366210938</v>
@@ -2076,11 +2088,11 @@
       <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B93" t="n">
-        <v>71.76964569091797</v>
+        <v>71.7696533203125</v>
       </c>
       <c r="C93" t="n">
         <v>77.58000183105469</v>
@@ -2093,11 +2105,11 @@
       <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B94" t="n">
-        <v>73.22390747070312</v>
+        <v>73.22391510009766</v>
       </c>
       <c r="C94" t="n">
         <v>79.01000213623047</v>
@@ -2110,11 +2122,11 @@
       <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B95" t="n">
-        <v>71.870849609375</v>
+        <v>71.87083435058594</v>
       </c>
       <c r="C95" t="n">
         <v>77.55000305175781</v>
@@ -2127,11 +2139,11 @@
       <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B96" t="n">
-        <v>69.034912109375</v>
+        <v>69.03492736816406</v>
       </c>
       <c r="C96" t="n">
         <v>74.48999786376953</v>
@@ -2144,11 +2156,11 @@
       <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B97" t="n">
-        <v>67.22106170654297</v>
+        <v>67.22105407714844</v>
       </c>
       <c r="C97" t="n">
         <v>72.38999938964844</v>
@@ -2161,7 +2173,7 @@
       <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B98" t="n">
@@ -2178,11 +2190,11 @@
       <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B99" t="n">
-        <v>71.72474670410156</v>
+        <v>71.72473907470703</v>
       </c>
       <c r="C99" t="n">
         <v>77.23999786376953</v>
@@ -2195,11 +2207,11 @@
       <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B100" t="n">
-        <v>73.43318176269531</v>
+        <v>73.43314361572266</v>
       </c>
       <c r="C100" t="n">
         <v>78.94000244140625</v>
@@ -2212,11 +2224,11 @@
       <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B101" t="n">
-        <v>68.99593353271484</v>
+        <v>68.99591827392578</v>
       </c>
       <c r="C101" t="n">
         <v>74.16999816894531</v>
@@ -2229,11 +2241,11 @@
       <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B102" t="n">
-        <v>72.60525512695312</v>
+        <v>72.60527038574219</v>
       </c>
       <c r="C102" t="n">
         <v>78.05000305175781</v>
@@ -2246,11 +2258,11 @@
       <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B103" t="n">
-        <v>75.38705444335938</v>
+        <v>75.38706970214844</v>
       </c>
       <c r="C103" t="n">
         <v>80.90000152587891</v>
@@ -2263,11 +2275,11 @@
       <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B104" t="n">
-        <v>77.06439208984375</v>
+        <v>77.06438446044922</v>
       </c>
       <c r="C104" t="n">
         <v>82.69999694824219</v>
@@ -2280,11 +2292,11 @@
       <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B105" t="n">
-        <v>76.88733673095703</v>
+        <v>76.8873291015625</v>
       </c>
       <c r="C105" t="n">
         <v>82.51000213623047</v>
@@ -2297,7 +2309,7 @@
       <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B106" t="n">
@@ -2314,11 +2326,11 @@
       <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B107" t="n">
-        <v>72.8563232421875</v>
+        <v>72.85630798339844</v>
       </c>
       <c r="C107" t="n">
         <v>78.01999664306641</v>
@@ -2331,7 +2343,7 @@
       <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B108" t="n">
@@ -2348,7 +2360,7 @@
       <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B109" t="n">
@@ -2365,11 +2377,11 @@
       <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B110" t="n">
-        <v>83.14616394042969</v>
+        <v>83.14617156982422</v>
       </c>
       <c r="C110" t="n">
         <v>88.87000274658203</v>
@@ -2382,11 +2394,11 @@
       <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B111" t="n">
-        <v>85.34480285644531</v>
+        <v>85.34483337402344</v>
       </c>
       <c r="C111" t="n">
         <v>91.22000122070312</v>
@@ -2399,11 +2411,11 @@
       <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B112" t="n">
-        <v>89.25464630126953</v>
+        <v>89.25466156005859</v>
       </c>
       <c r="C112" t="n">
         <v>95.23000335693359</v>
@@ -2416,11 +2428,11 @@
       <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B113" t="n">
-        <v>87.8956298828125</v>
+        <v>87.89562225341797</v>
       </c>
       <c r="C113" t="n">
         <v>93.77999877929688</v>
@@ -2433,11 +2445,11 @@
       <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B114" t="n">
-        <v>93.31294250488281</v>
+        <v>93.31295776367188</v>
       </c>
       <c r="C114" t="n">
         <v>99.55999755859375</v>
@@ -2450,11 +2462,11 @@
       <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B115" t="n">
-        <v>97.18070220947266</v>
+        <v>97.18070983886719</v>
       </c>
       <c r="C115" t="n">
         <v>103.5199966430664</v>
@@ -2467,11 +2479,11 @@
       <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B116" t="n">
-        <v>98.79537963867188</v>
+        <v>98.79539489746094</v>
       </c>
       <c r="C116" t="n">
         <v>105.2399978637695</v>
@@ -2484,7 +2496,7 @@
       <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B117" t="n">
@@ -2501,11 +2513,11 @@
       <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B118" t="n">
-        <v>105.8825759887695</v>
+        <v>105.882568359375</v>
       </c>
       <c r="C118" t="n">
         <v>112.5899963378906</v>
@@ -2518,11 +2530,11 @@
       <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B119" t="n">
-        <v>107.2273788452148</v>
+        <v>107.2273864746094</v>
       </c>
       <c r="C119" t="n">
         <v>114.0199966430664</v>
@@ -2535,11 +2547,11 @@
       <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B120" t="n">
-        <v>116.8291320800781</v>
+        <v>116.8291397094727</v>
       </c>
       <c r="C120" t="n">
         <v>124.2300033569336</v>
@@ -2552,7 +2564,7 @@
       <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B121" t="n">
@@ -2569,11 +2581,11 @@
       <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B122" t="n">
-        <v>112.6896362304688</v>
+        <v>112.6896209716797</v>
       </c>
       <c r="C122" t="n">
         <v>119.620002746582</v>
@@ -2586,11 +2598,11 @@
       <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B123" t="n">
-        <v>119.5289916992188</v>
+        <v>119.5289840698242</v>
       </c>
       <c r="C123" t="n">
         <v>126.879997253418</v>
@@ -2603,11 +2615,11 @@
       <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B124" t="n">
-        <v>123.3444366455078</v>
+        <v>123.3443908691406</v>
       </c>
       <c r="C124" t="n">
         <v>130.7200012207031</v>
@@ -2620,11 +2632,11 @@
       <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B125" t="n">
-        <v>124.976806640625</v>
+        <v>124.9768142700195</v>
       </c>
       <c r="C125" t="n">
         <v>132.4499969482422</v>
@@ -2637,7 +2649,7 @@
       <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B126" t="n">
@@ -2654,11 +2666,11 @@
       <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B127" t="n">
-        <v>138.8104095458984</v>
+        <v>138.8103790283203</v>
       </c>
       <c r="C127" t="n">
         <v>146.8899993896484</v>
@@ -2671,11 +2683,11 @@
       <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B128" t="n">
-        <v>141.8343658447266</v>
+        <v>141.8343811035156</v>
       </c>
       <c r="C128" t="n">
         <v>150.0899963378906</v>
@@ -2688,11 +2700,11 @@
       <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B129" t="n">
-        <v>130.2676086425781</v>
+        <v>130.2675933837891</v>
       </c>
       <c r="C129" t="n">
         <v>137.8500061035156</v>
@@ -2705,7 +2717,7 @@
       <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B130" t="n">
@@ -2722,11 +2734,11 @@
       <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B131" t="n">
-        <v>124.9065551757812</v>
+        <v>124.9065628051758</v>
       </c>
       <c r="C131" t="n">
         <v>131.9400024414062</v>
@@ -2739,11 +2751,11 @@
       <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B132" t="n">
-        <v>127.8129272460938</v>
+        <v>127.8129043579102</v>
       </c>
       <c r="C132" t="n">
         <v>135.0099945068359</v>
@@ -2756,11 +2768,11 @@
       <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B133" t="n">
-        <v>140.4687805175781</v>
+        <v>140.4687652587891</v>
       </c>
       <c r="C133" t="n">
         <v>148.1199951171875</v>
@@ -2773,7 +2785,7 @@
       <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B134" t="n">
@@ -2790,11 +2802,11 @@
       <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B135" t="n">
-        <v>155.9362182617188</v>
+        <v>155.9363098144531</v>
       </c>
       <c r="C135" t="n">
         <v>164.4299926757812</v>
@@ -2807,7 +2819,7 @@
       <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B136" t="n">
@@ -2824,11 +2836,11 @@
       <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B137" t="n">
-        <v>164.8383026123047</v>
+        <v>164.8383331298828</v>
       </c>
       <c r="C137" t="n">
         <v>173.5500030517578</v>
@@ -2841,11 +2853,11 @@
       <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B138" t="n">
-        <v>169.0649261474609</v>
+        <v>169.0649566650391</v>
       </c>
       <c r="C138" t="n">
         <v>178</v>
@@ -2858,11 +2870,11 @@
       <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B139" t="n">
-        <v>171.9912109375</v>
+        <v>171.9912567138672</v>
       </c>
       <c r="C139" t="n">
         <v>180.8200073242188</v>
@@ -2875,7 +2887,7 @@
       <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B140" t="n">
@@ -2892,11 +2904,11 @@
       <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B141" t="n">
-        <v>170.1269226074219</v>
+        <v>170.1269073486328</v>
       </c>
       <c r="C141" t="n">
         <v>178.8600006103516</v>
@@ -2909,11 +2921,11 @@
       <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B142" t="n">
-        <v>175.7950134277344</v>
+        <v>175.7949981689453</v>
       </c>
       <c r="C142" t="n">
         <v>184.5099945068359</v>
@@ -2926,7 +2938,7 @@
       <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B143" t="n">
@@ -2943,11 +2955,11 @@
       <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B144" t="n">
-        <v>189.5719909667969</v>
+        <v>189.5720062255859</v>
       </c>
       <c r="C144" t="n">
         <v>198.9700012207031</v>
@@ -2960,11 +2972,11 @@
       <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B145" t="n">
-        <v>173.4257049560547</v>
+        <v>173.4257354736328</v>
       </c>
       <c r="C145" t="n">
         <v>181.7599945068359</v>
@@ -2977,11 +2989,11 @@
       <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B146" t="n">
-        <v>153.7321014404297</v>
+        <v>153.7321319580078</v>
       </c>
       <c r="C146" t="n">
         <v>161.1199951171875</v>
@@ -2994,11 +3006,11 @@
       <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B147" t="n">
-        <v>170.5250549316406</v>
+        <v>170.5251007080078</v>
       </c>
       <c r="C147" t="n">
         <v>178.7200012207031</v>
@@ -3011,11 +3023,11 @@
       <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B148" t="n">
-        <v>186.5995330810547</v>
+        <v>186.5995635986328</v>
       </c>
       <c r="C148" t="n">
         <v>195.2400054931641</v>
@@ -3028,11 +3040,11 @@
       <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B149" t="n">
-        <v>184.6211242675781</v>
+        <v>184.6211395263672</v>
       </c>
       <c r="C149" t="n">
         <v>193.1699981689453</v>
@@ -3045,7 +3057,7 @@
       <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B150" t="n">
@@ -3062,11 +3074,11 @@
       <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B151" t="n">
-        <v>202.9145355224609</v>
+        <v>202.9145202636719</v>
       </c>
       <c r="C151" t="n">
         <v>211.9900054931641</v>
@@ -3079,11 +3091,11 @@
       <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B152" t="n">
-        <v>191.4091491699219</v>
+        <v>191.4091033935547</v>
       </c>
       <c r="C152" t="n">
         <v>199.9700012207031</v>
@@ -3096,11 +3108,11 @@
       <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B153" t="n">
-        <v>173.9308013916016</v>
+        <v>173.9308319091797</v>
       </c>
       <c r="C153" t="n">
         <v>181.7100067138672</v>
@@ -3113,11 +3125,11 @@
       <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B154" t="n">
-        <v>201.6481475830078</v>
+        <v>201.6481323242188</v>
       </c>
       <c r="C154" t="n">
         <v>210.3500061035156</v>
@@ -3130,11 +3142,11 @@
       <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B155" t="n">
-        <v>209.6814270019531</v>
+        <v>209.6814422607422</v>
       </c>
       <c r="C155" t="n">
         <v>218.7299957275391</v>
@@ -3147,11 +3159,11 @@
       <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B156" t="n">
-        <v>185.2555084228516</v>
+        <v>185.2555236816406</v>
       </c>
       <c r="C156" t="n">
         <v>193.25</v>
@@ -3164,11 +3176,11 @@
       <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B157" t="n">
-        <v>203.9197998046875</v>
+        <v>203.9197845458984</v>
       </c>
       <c r="C157" t="n">
         <v>212.3899993896484</v>
@@ -3181,11 +3193,11 @@
       <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B158" t="n">
-        <v>203.2861328125</v>
+        <v>203.2860870361328</v>
       </c>
       <c r="C158" t="n">
         <v>211.7299957275391</v>
@@ -3198,11 +3210,11 @@
       <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B159" t="n">
-        <v>224.2455596923828</v>
+        <v>224.2455444335938</v>
       </c>
       <c r="C159" t="n">
         <v>233.5599975585938</v>
@@ -3215,11 +3227,11 @@
       <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B160" t="n">
-        <v>218.5521697998047</v>
+        <v>218.5522003173828</v>
       </c>
       <c r="C160" t="n">
         <v>227.3000030517578</v>
@@ -3232,11 +3244,11 @@
       <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B161" t="n">
-        <v>224.8212432861328</v>
+        <v>224.8212890625</v>
       </c>
       <c r="C161" t="n">
         <v>233.8200073242188</v>
@@ -3249,11 +3261,11 @@
       <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B162" t="n">
-        <v>236.9075012207031</v>
+        <v>236.9074859619141</v>
       </c>
       <c r="C162" t="n">
         <v>246.3899993896484</v>
@@ -3266,11 +3278,11 @@
       <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B163" t="n">
-        <v>220.5832214355469</v>
+        <v>220.5832061767578</v>
       </c>
       <c r="C163" t="n">
         <v>229.1000061035156</v>
@@ -3283,11 +3295,11 @@
       <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B164" t="n">
-        <v>214.4692993164062</v>
+        <v>214.4692687988281</v>
       </c>
       <c r="C164" t="n">
         <v>222.75</v>
@@ -3300,7 +3312,7 @@
       <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B165" t="n">
@@ -3317,11 +3329,11 @@
       <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B166" t="n">
-        <v>186.8950347900391</v>
+        <v>186.8950500488281</v>
       </c>
       <c r="C166" t="n">
         <v>193.7700042724609</v>
@@ -3334,11 +3346,11 @@
       <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B167" t="n">
-        <v>209.0211639404297</v>
+        <v>209.0211029052734</v>
       </c>
       <c r="C167" t="n">
         <v>216.7100067138672</v>
@@ -3351,11 +3363,11 @@
       <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B168" t="n">
-        <v>218.1454772949219</v>
+        <v>218.1454925537109</v>
       </c>
       <c r="C168" t="n">
         <v>226.1699981689453</v>
@@ -3368,11 +3380,11 @@
       <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B169" t="n">
-        <v>208.7911987304688</v>
+        <v>208.7911834716797</v>
       </c>
       <c r="C169" t="n">
         <v>216.1199951171875</v>
@@ -3385,11 +3397,11 @@
       <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B170" t="n">
-        <v>214.2495727539062</v>
+        <v>214.2495880126953</v>
       </c>
       <c r="C170" t="n">
         <v>221.7700042724609</v>
@@ -3402,11 +3414,11 @@
       <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B171" t="n">
-        <v>205.902587890625</v>
+        <v>205.9026184082031</v>
       </c>
       <c r="C171" t="n">
         <v>213.1300048828125</v>
@@ -3419,11 +3431,11 @@
       <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B172" t="n">
-        <v>205.3666229248047</v>
+        <v>205.3666076660156</v>
       </c>
       <c r="C172" t="n">
         <v>212.1699981689453</v>
@@ -3436,11 +3448,11 @@
       <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B173" t="n">
-        <v>190.5766143798828</v>
+        <v>190.5765838623047</v>
       </c>
       <c r="C173" t="n">
         <v>196.8899993896484</v>
@@ -3453,7 +3465,7 @@
       <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B174" t="n">
@@ -3470,11 +3482,11 @@
       <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B175" t="n">
-        <v>192.6789093017578</v>
+        <v>192.6788940429688</v>
       </c>
       <c r="C175" t="n">
         <v>198.7100067138672</v>
@@ -3487,11 +3499,11 @@
       <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B176" t="n">
-        <v>172.2581024169922</v>
+        <v>172.258056640625</v>
       </c>
       <c r="C176" t="n">
         <v>177.6499938964844</v>
@@ -3504,11 +3516,11 @@
       <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B177" t="n">
-        <v>200.8724212646484</v>
+        <v>200.8724670410156</v>
       </c>
       <c r="C177" t="n">
         <v>207.1600036621094</v>
@@ -3521,7 +3533,7 @@
       <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B178" t="n">
@@ -3538,11 +3550,11 @@
       <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B179" t="n">
-        <v>201.9044952392578</v>
+        <v>201.9045257568359</v>
       </c>
       <c r="C179" t="n">
         <v>207.7599945068359</v>
@@ -3555,7 +3567,7 @@
       <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B180" t="n">
@@ -3572,11 +3584,11 @@
       <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B181" t="n">
-        <v>214.1598663330078</v>
+        <v>214.1598358154297</v>
       </c>
       <c r="C181" t="n">
         <v>219.9400024414062</v>
@@ -3589,7 +3601,7 @@
       <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B182" t="n">
@@ -3606,11 +3618,11 @@
       <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B183" t="n">
-        <v>226.6136932373047</v>
+        <v>226.6137390136719</v>
       </c>
       <c r="C183" t="n">
         <v>232.7299957275391</v>
@@ -3623,11 +3635,11 @@
       <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B184" t="n">
-        <v>215.6408081054688</v>
+        <v>215.6407775878906</v>
       </c>
       <c r="C184" t="n">
         <v>221.0299987792969</v>
@@ -3640,7 +3652,7 @@
       <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B185" t="n">
@@ -3657,7 +3669,7 @@
       <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B186" t="n">
@@ -3674,11 +3686,11 @@
       <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B187" t="n">
-        <v>240.1404724121094</v>
+        <v>240.1405181884766</v>
       </c>
       <c r="C187" t="n">
         <v>245.6799926757812</v>
@@ -3691,11 +3703,11 @@
       <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B188" t="n">
-        <v>224.8238220214844</v>
+        <v>224.8238372802734</v>
       </c>
       <c r="C188" t="n">
         <v>230.0099945068359</v>
@@ -3708,11 +3720,11 @@
       <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B189" t="n">
-        <v>229.799072265625</v>
+        <v>229.7990570068359</v>
       </c>
       <c r="C189" t="n">
         <v>235.1000061035156</v>
@@ -3725,11 +3737,11 @@
       <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B190" t="n">
-        <v>251.4265747070312</v>
+        <v>251.4266052246094</v>
       </c>
       <c r="C190" t="n">
         <v>256.6799926757812</v>
@@ -3742,11 +3754,11 @@
       <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B191" t="n">
-        <v>255.0214691162109</v>
+        <v>255.0215454101562</v>
       </c>
       <c r="C191" t="n">
         <v>260.3500061035156</v>
@@ -3759,11 +3771,11 @@
       <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B192" t="n">
-        <v>267.6672973632812</v>
+        <v>267.6673278808594</v>
       </c>
       <c r="C192" t="n">
         <v>273.260009765625</v>
@@ -3776,7 +3788,7 @@
       <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B193" t="n">
@@ -3793,7 +3805,7 @@
       <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B194" t="n">
@@ -3810,11 +3822,11 @@
       <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B195" t="n">
-        <v>263.6030883789062</v>
+        <v>263.6030578613281</v>
       </c>
       <c r="C195" t="n">
         <v>268.6099853515625</v>
@@ -3827,7 +3839,7 @@
       <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B196" t="n">
@@ -3844,11 +3856,11 @@
       <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B197" t="n">
-        <v>258.0542297363281</v>
+        <v>258.05419921875</v>
       </c>
       <c r="C197" t="n">
         <v>262.4700012207031</v>
@@ -3861,11 +3873,11 @@
       <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B198" t="n">
-        <v>261.2003784179688</v>
+        <v>261.200439453125</v>
       </c>
       <c r="C198" t="n">
         <v>265.6700134277344</v>
@@ -3878,7 +3890,7 @@
       <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B199" t="n">
@@ -3895,11 +3907,11 @@
       <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B200" t="n">
-        <v>270.8663330078125</v>
+        <v>270.8663635253906</v>
       </c>
       <c r="C200" t="n">
         <v>274.9500122070312</v>
@@ -3912,11 +3924,11 @@
       <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B201" t="n">
-        <v>285.5450744628906</v>
+        <v>285.5450439453125</v>
       </c>
       <c r="C201" t="n">
         <v>289.8500061035156</v>
@@ -3929,11 +3941,11 @@
       <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B202" t="n">
-        <v>310.9904174804688</v>
+        <v>310.9904479980469</v>
       </c>
       <c r="C202" t="n">
         <v>315.0799865722656</v>
@@ -3946,7 +3958,7 @@
       <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B203" t="n">
@@ -3963,7 +3975,7 @@
       <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B204" t="n">
@@ -3980,7 +3992,7 @@
       <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B205" t="n">
@@ -3997,7 +4009,7 @@
       <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B206" t="n">
@@ -4014,11 +4026,11 @@
       <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B207" t="n">
-        <v>341.5894165039062</v>
+        <v>341.5893859863281</v>
       </c>
       <c r="C207" t="n">
         <v>345.5</v>
@@ -4031,7 +4043,7 @@
       <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B208" t="n">
@@ -4048,11 +4060,11 @@
       <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B209" t="n">
-        <v>351.6143188476562</v>
+        <v>351.6142883300781</v>
       </c>
       <c r="C209" t="n">
         <v>355.0499877929688</v>
@@ -4065,11 +4077,11 @@
       <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B210" t="n">
-        <v>342.1270141601562</v>
+        <v>342.1269836425781</v>
       </c>
       <c r="C210" t="n">
         <v>345.4700012207031</v>
@@ -4082,11 +4094,11 @@
       <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B211" t="n">
-        <v>348.9889221191406</v>
+        <v>348.9889526367188</v>
       </c>
       <c r="C211" t="n">
         <v>351.7799987792969</v>
@@ -4099,7 +4111,7 @@
       <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B212" t="n">
@@ -4116,11 +4128,11 @@
       <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B213" t="n">
-        <v>338.0365295410156</v>
+        <v>338.0364990234375</v>
       </c>
       <c r="C213" t="n">
         <v>340.739990234375</v>
@@ -4133,7 +4145,7 @@
       <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B214" t="n">
@@ -4150,7 +4162,7 @@
       <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B215" t="n">
@@ -4167,7 +4179,7 @@
       <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B216" t="n">
@@ -4184,7 +4196,7 @@
       <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B217" t="n">
@@ -4201,7 +4213,7 @@
       <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B218" t="n">
@@ -4218,7 +4230,7 @@
       <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B219" t="n">
@@ -4235,7 +4247,7 @@
       <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B220" t="n">
@@ -4252,7 +4264,7 @@
       <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B221" t="n">
@@ -4269,7 +4281,7 @@
       <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B222" t="n">
@@ -4286,7 +4298,7 @@
       <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B223" t="n">
@@ -4303,17 +4315,17 @@
       <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B224" t="n">
-        <v>361.5199890136719</v>
+        <v>367.9800109863281</v>
       </c>
       <c r="C224" t="n">
-        <v>361.5199890136719</v>
+        <v>367.9800109863281</v>
       </c>
       <c r="D224" t="n">
-        <v>100388600</v>
+        <v>104804100</v>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
@@ -4344,52 +4356,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40130</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40137</v>
       </c>
       <c r="C2" t="n">
@@ -4418,10 +4430,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40205</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40212</v>
       </c>
       <c r="C3" t="n">
@@ -4468,12 +4480,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/V.xlsx
+++ b/salidas/empresas/V.xlsx
@@ -485,7 +485,7 @@
         <v>39538</v>
       </c>
       <c r="B2" t="n">
-        <v>13.6785249710083</v>
+        <v>13.67852783203125</v>
       </c>
       <c r="C2" t="n">
         <v>15.59000015258789</v>
@@ -502,7 +502,7 @@
         <v>39568</v>
       </c>
       <c r="B3" t="n">
-        <v>18.3045654296875</v>
+        <v>18.3045711517334</v>
       </c>
       <c r="C3" t="n">
         <v>20.86249923706055</v>
@@ -519,7 +519,7 @@
         <v>39599</v>
       </c>
       <c r="B4" t="n">
-        <v>18.94286727905273</v>
+        <v>18.94287109375</v>
       </c>
       <c r="C4" t="n">
         <v>21.59000015258789</v>
@@ -536,7 +536,7 @@
         <v>39629</v>
       </c>
       <c r="B5" t="n">
-        <v>17.83516311645508</v>
+        <v>17.83517646789551</v>
       </c>
       <c r="C5" t="n">
         <v>20.32749938964844</v>
@@ -553,7 +553,7 @@
         <v>39660</v>
       </c>
       <c r="B6" t="n">
-        <v>16.02555465698242</v>
+        <v>16.02554321289062</v>
       </c>
       <c r="C6" t="n">
         <v>18.26499938964844</v>
@@ -570,7 +570,7 @@
         <v>39691</v>
       </c>
       <c r="B7" t="n">
-        <v>16.67253875732422</v>
+        <v>16.67253684997559</v>
       </c>
       <c r="C7" t="n">
         <v>18.97500038146973</v>
@@ -587,7 +587,7 @@
         <v>39721</v>
       </c>
       <c r="B8" t="n">
-        <v>13.48520851135254</v>
+        <v>13.48520946502686</v>
       </c>
       <c r="C8" t="n">
         <v>15.34749984741211</v>
@@ -604,7 +604,7 @@
         <v>39752</v>
       </c>
       <c r="B9" t="n">
-        <v>12.15843486785889</v>
+        <v>12.15843105316162</v>
       </c>
       <c r="C9" t="n">
         <v>13.83749961853027</v>
@@ -621,7 +621,7 @@
         <v>39782</v>
       </c>
       <c r="B10" t="n">
-        <v>11.56815242767334</v>
+        <v>11.56815338134766</v>
       </c>
       <c r="C10" t="n">
         <v>13.14000034332275</v>
@@ -638,7 +638,7 @@
         <v>39813</v>
       </c>
       <c r="B11" t="n">
-        <v>11.54394435882568</v>
+        <v>11.5439453125</v>
       </c>
       <c r="C11" t="n">
         <v>13.11250019073486</v>
@@ -655,7 +655,7 @@
         <v>39844</v>
       </c>
       <c r="B12" t="n">
-        <v>10.86165046691895</v>
+        <v>10.86164665222168</v>
       </c>
       <c r="C12" t="n">
         <v>12.33749961853027</v>
@@ -672,7 +672,7 @@
         <v>39872</v>
       </c>
       <c r="B13" t="n">
-        <v>12.50592708587646</v>
+        <v>12.50592994689941</v>
       </c>
       <c r="C13" t="n">
         <v>14.17749977111816</v>
@@ -689,7 +689,7 @@
         <v>39903</v>
       </c>
       <c r="B14" t="n">
-        <v>12.26114940643311</v>
+        <v>12.26114654541016</v>
       </c>
       <c r="C14" t="n">
         <v>13.89999961853027</v>
@@ -706,7 +706,7 @@
         <v>39933</v>
       </c>
       <c r="B15" t="n">
-        <v>14.32525062561035</v>
+        <v>14.32525730133057</v>
       </c>
       <c r="C15" t="n">
         <v>16.23999977111816</v>
@@ -723,7 +723,7 @@
         <v>39964</v>
       </c>
       <c r="B16" t="n">
-        <v>14.95577239990234</v>
+        <v>14.95577430725098</v>
       </c>
       <c r="C16" t="n">
         <v>16.92749977111816</v>
@@ -740,7 +740,7 @@
         <v>39994</v>
       </c>
       <c r="B17" t="n">
-        <v>13.75197410583496</v>
+        <v>13.75197505950928</v>
       </c>
       <c r="C17" t="n">
         <v>15.5649995803833</v>
@@ -757,7 +757,7 @@
         <v>40025</v>
       </c>
       <c r="B18" t="n">
-        <v>14.4587926864624</v>
+        <v>14.45879077911377</v>
       </c>
       <c r="C18" t="n">
         <v>16.36499977111816</v>
@@ -774,7 +774,7 @@
         <v>40056</v>
       </c>
       <c r="B19" t="n">
-        <v>15.72862529754639</v>
+        <v>15.72862720489502</v>
       </c>
       <c r="C19" t="n">
         <v>17.77499961853027</v>
@@ -791,7 +791,7 @@
         <v>40086</v>
       </c>
       <c r="B20" t="n">
-        <v>15.28840732574463</v>
+        <v>15.28839874267578</v>
       </c>
       <c r="C20" t="n">
         <v>17.27750015258789</v>
@@ -808,7 +808,7 @@
         <v>40117</v>
       </c>
       <c r="B21" t="n">
-        <v>16.75950622558594</v>
+        <v>16.75950241088867</v>
       </c>
       <c r="C21" t="n">
         <v>18.94000053405762</v>
@@ -848,7 +848,7 @@
         <v>40178</v>
       </c>
       <c r="B23" t="n">
-        <v>19.37772750854492</v>
+        <v>19.37772560119629</v>
       </c>
       <c r="C23" t="n">
         <v>21.86499977111816</v>
@@ -871,7 +871,7 @@
         <v>40209</v>
       </c>
       <c r="B24" t="n">
-        <v>18.17464828491211</v>
+        <v>18.17465591430664</v>
       </c>
       <c r="C24" t="n">
         <v>20.50749969482422</v>
@@ -894,7 +894,7 @@
         <v>40237</v>
       </c>
       <c r="B25" t="n">
-        <v>18.92313194274902</v>
+        <v>18.92312622070312</v>
       </c>
       <c r="C25" t="n">
         <v>21.31999969482422</v>
@@ -917,7 +917,7 @@
         <v>40268</v>
       </c>
       <c r="B26" t="n">
-        <v>20.19902420043945</v>
+        <v>20.19902229309082</v>
       </c>
       <c r="C26" t="n">
         <v>22.75749969482422</v>
@@ -940,7 +940,7 @@
         <v>40298</v>
       </c>
       <c r="B27" t="n">
-        <v>20.02150535583496</v>
+        <v>20.02150917053223</v>
       </c>
       <c r="C27" t="n">
         <v>22.5575008392334</v>
@@ -963,7 +963,7 @@
         <v>40329</v>
       </c>
       <c r="B28" t="n">
-        <v>16.10237503051758</v>
+        <v>16.10236167907715</v>
       </c>
       <c r="C28" t="n">
         <v>18.11499977111816</v>
@@ -986,7 +986,7 @@
         <v>40359</v>
       </c>
       <c r="B29" t="n">
-        <v>15.7223596572876</v>
+        <v>15.72236061096191</v>
       </c>
       <c r="C29" t="n">
         <v>17.6875</v>
@@ -1009,7 +1009,7 @@
         <v>40390</v>
       </c>
       <c r="B30" t="n">
-        <v>16.30014419555664</v>
+        <v>16.30013465881348</v>
       </c>
       <c r="C30" t="n">
         <v>18.33749961853027</v>
@@ -1032,7 +1032,7 @@
         <v>40421</v>
       </c>
       <c r="B31" t="n">
-        <v>15.35452842712402</v>
+        <v>15.35453033447266</v>
       </c>
       <c r="C31" t="n">
         <v>17.2450008392334</v>
@@ -1072,7 +1072,7 @@
         <v>40482</v>
       </c>
       <c r="B33" t="n">
-        <v>17.3979320526123</v>
+        <v>17.39793968200684</v>
       </c>
       <c r="C33" t="n">
         <v>19.54000091552734</v>
@@ -1089,7 +1089,7 @@
         <v>40512</v>
       </c>
       <c r="B34" t="n">
-        <v>16.47150230407715</v>
+        <v>16.47150802612305</v>
       </c>
       <c r="C34" t="n">
         <v>18.46249961853027</v>
@@ -1106,7 +1106,7 @@
         <v>40543</v>
       </c>
       <c r="B35" t="n">
-        <v>15.69755554199219</v>
+        <v>15.69755744934082</v>
       </c>
       <c r="C35" t="n">
         <v>17.59499931335449</v>
@@ -1140,7 +1140,7 @@
         <v>40602</v>
       </c>
       <c r="B37" t="n">
-        <v>16.32590866088867</v>
+        <v>16.32591247558594</v>
       </c>
       <c r="C37" t="n">
         <v>18.26250076293945</v>
@@ -1157,7 +1157,7 @@
         <v>40633</v>
       </c>
       <c r="B38" t="n">
-        <v>16.45330238342285</v>
+        <v>16.45329666137695</v>
       </c>
       <c r="C38" t="n">
         <v>18.40500068664551</v>
@@ -1174,7 +1174,7 @@
         <v>40663</v>
       </c>
       <c r="B39" t="n">
-        <v>17.4590015411377</v>
+        <v>17.45900535583496</v>
       </c>
       <c r="C39" t="n">
         <v>19.53000068664551</v>
@@ -1225,7 +1225,7 @@
         <v>40755</v>
       </c>
       <c r="B42" t="n">
-        <v>19.15294456481934</v>
+        <v>19.1529483795166</v>
       </c>
       <c r="C42" t="n">
         <v>21.38500022888184</v>
@@ -1242,7 +1242,7 @@
         <v>40786</v>
       </c>
       <c r="B43" t="n">
-        <v>19.71133995056152</v>
+        <v>19.71132469177246</v>
       </c>
       <c r="C43" t="n">
         <v>21.96999931335449</v>
@@ -1259,7 +1259,7 @@
         <v>40816</v>
       </c>
       <c r="B44" t="n">
-        <v>19.22685050964355</v>
+        <v>19.22683906555176</v>
       </c>
       <c r="C44" t="n">
         <v>21.43000030517578</v>
@@ -1276,7 +1276,7 @@
         <v>40847</v>
       </c>
       <c r="B45" t="n">
-        <v>20.91806602478027</v>
+        <v>20.91805267333984</v>
       </c>
       <c r="C45" t="n">
         <v>23.31500053405762</v>
@@ -1293,7 +1293,7 @@
         <v>40877</v>
       </c>
       <c r="B46" t="n">
-        <v>21.80035972595215</v>
+        <v>21.80035591125488</v>
       </c>
       <c r="C46" t="n">
         <v>24.24250030517578</v>
@@ -1310,7 +1310,7 @@
         <v>40908</v>
       </c>
       <c r="B47" t="n">
-        <v>22.82551383972168</v>
+        <v>22.82551193237305</v>
       </c>
       <c r="C47" t="n">
         <v>25.38249969482422</v>
@@ -1327,7 +1327,7 @@
         <v>40939</v>
       </c>
       <c r="B48" t="n">
-        <v>22.62542533874512</v>
+        <v>22.62543106079102</v>
       </c>
       <c r="C48" t="n">
         <v>25.15999984741211</v>
@@ -1344,7 +1344,7 @@
         <v>40968</v>
       </c>
       <c r="B49" t="n">
-        <v>26.21181297302246</v>
+        <v>26.21181678771973</v>
       </c>
       <c r="C49" t="n">
         <v>29.09250068664551</v>
@@ -1361,7 +1361,7 @@
         <v>40999</v>
       </c>
       <c r="B50" t="n">
-        <v>26.57897186279297</v>
+        <v>26.57896995544434</v>
       </c>
       <c r="C50" t="n">
         <v>29.5</v>
@@ -1378,7 +1378,7 @@
         <v>41029</v>
       </c>
       <c r="B51" t="n">
-        <v>27.7006893157959</v>
+        <v>27.70068550109863</v>
       </c>
       <c r="C51" t="n">
         <v>30.7450008392334</v>
@@ -1412,7 +1412,7 @@
         <v>41090</v>
       </c>
       <c r="B53" t="n">
-        <v>27.89973258972168</v>
+        <v>27.89973068237305</v>
       </c>
       <c r="C53" t="n">
         <v>30.90749931335449</v>
@@ -1429,7 +1429,7 @@
         <v>41121</v>
       </c>
       <c r="B54" t="n">
-        <v>29.12738037109375</v>
+        <v>29.12738227844238</v>
       </c>
       <c r="C54" t="n">
         <v>32.26750183105469</v>
@@ -1446,7 +1446,7 @@
         <v>41152</v>
       </c>
       <c r="B55" t="n">
-        <v>28.99144172668457</v>
+        <v>28.99143981933594</v>
       </c>
       <c r="C55" t="n">
         <v>32.0625</v>
@@ -1463,7 +1463,7 @@
         <v>41182</v>
       </c>
       <c r="B56" t="n">
-        <v>30.35453033447266</v>
+        <v>30.35453605651855</v>
       </c>
       <c r="C56" t="n">
         <v>33.56999969482422</v>
@@ -1514,7 +1514,7 @@
         <v>41274</v>
       </c>
       <c r="B59" t="n">
-        <v>34.34484100341797</v>
+        <v>34.34482955932617</v>
       </c>
       <c r="C59" t="n">
         <v>37.89500045776367</v>
@@ -1531,7 +1531,7 @@
         <v>41305</v>
       </c>
       <c r="B60" t="n">
-        <v>35.77907943725586</v>
+        <v>35.77909851074219</v>
       </c>
       <c r="C60" t="n">
         <v>39.47750091552734</v>
@@ -1548,7 +1548,7 @@
         <v>41333</v>
       </c>
       <c r="B61" t="n">
-        <v>36.02029418945312</v>
+        <v>36.02030181884766</v>
       </c>
       <c r="C61" t="n">
         <v>39.65999984741211</v>
@@ -1565,7 +1565,7 @@
         <v>41364</v>
       </c>
       <c r="B62" t="n">
-        <v>38.56333923339844</v>
+        <v>38.56333160400391</v>
       </c>
       <c r="C62" t="n">
         <v>42.45999908447266</v>
@@ -1582,7 +1582,7 @@
         <v>41394</v>
       </c>
       <c r="B63" t="n">
-        <v>38.2499885559082</v>
+        <v>38.25000762939453</v>
       </c>
       <c r="C63" t="n">
         <v>42.1150016784668</v>
@@ -1599,7 +1599,7 @@
         <v>41425</v>
       </c>
       <c r="B64" t="n">
-        <v>40.52207183837891</v>
+        <v>40.52207565307617</v>
       </c>
       <c r="C64" t="n">
         <v>44.53499984741211</v>
@@ -1616,7 +1616,7 @@
         <v>41455</v>
       </c>
       <c r="B65" t="n">
-        <v>41.57071685791016</v>
+        <v>41.57073211669922</v>
       </c>
       <c r="C65" t="n">
         <v>45.6875</v>
@@ -1650,7 +1650,7 @@
         <v>41517</v>
       </c>
       <c r="B67" t="n">
-        <v>39.74906158447266</v>
+        <v>39.74905395507812</v>
       </c>
       <c r="C67" t="n">
         <v>43.60499954223633</v>
@@ -1667,7 +1667,7 @@
         <v>41547</v>
       </c>
       <c r="B68" t="n">
-        <v>43.55029296875</v>
+        <v>43.5503044128418</v>
       </c>
       <c r="C68" t="n">
         <v>47.77500152587891</v>
@@ -1684,7 +1684,7 @@
         <v>41578</v>
       </c>
       <c r="B69" t="n">
-        <v>44.81966018676758</v>
+        <v>44.81967163085938</v>
       </c>
       <c r="C69" t="n">
         <v>49.16749954223633</v>
@@ -1701,7 +1701,7 @@
         <v>41608</v>
       </c>
       <c r="B70" t="n">
-        <v>46.46078872680664</v>
+        <v>46.46079635620117</v>
       </c>
       <c r="C70" t="n">
         <v>50.8650016784668</v>
@@ -1718,7 +1718,7 @@
         <v>41639</v>
       </c>
       <c r="B71" t="n">
-        <v>50.8497428894043</v>
+        <v>50.84974670410156</v>
       </c>
       <c r="C71" t="n">
         <v>55.66999816894531</v>
@@ -1735,7 +1735,7 @@
         <v>41670</v>
       </c>
       <c r="B72" t="n">
-        <v>49.19418334960938</v>
+        <v>49.19417190551758</v>
       </c>
       <c r="C72" t="n">
         <v>53.85749816894531</v>
@@ -1803,7 +1803,7 @@
         <v>41790</v>
       </c>
       <c r="B76" t="n">
-        <v>49.23847198486328</v>
+        <v>49.23846435546875</v>
       </c>
       <c r="C76" t="n">
         <v>53.70750045776367</v>
@@ -1820,7 +1820,7 @@
         <v>41820</v>
       </c>
       <c r="B77" t="n">
-        <v>48.29418182373047</v>
+        <v>48.29417419433594</v>
       </c>
       <c r="C77" t="n">
         <v>52.6775016784668</v>
@@ -1837,7 +1837,7 @@
         <v>41851</v>
       </c>
       <c r="B78" t="n">
-        <v>48.36294174194336</v>
+        <v>48.36293792724609</v>
       </c>
       <c r="C78" t="n">
         <v>52.75249862670898</v>
@@ -1854,7 +1854,7 @@
         <v>41882</v>
       </c>
       <c r="B79" t="n">
-        <v>48.80183410644531</v>
+        <v>48.80184173583984</v>
       </c>
       <c r="C79" t="n">
         <v>53.13000106811523</v>
@@ -1871,7 +1871,7 @@
         <v>41912</v>
       </c>
       <c r="B80" t="n">
-        <v>48.99703216552734</v>
+        <v>48.99702835083008</v>
       </c>
       <c r="C80" t="n">
         <v>53.34249877929688</v>
@@ -1888,7 +1888,7 @@
         <v>41943</v>
       </c>
       <c r="B81" t="n">
-        <v>55.4405632019043</v>
+        <v>55.4405517578125</v>
       </c>
       <c r="C81" t="n">
         <v>60.35749816894531</v>
@@ -1905,7 +1905,7 @@
         <v>41973</v>
       </c>
       <c r="B82" t="n">
-        <v>59.40341949462891</v>
+        <v>59.40341567993164</v>
       </c>
       <c r="C82" t="n">
         <v>64.54750061035156</v>
@@ -1922,7 +1922,7 @@
         <v>42004</v>
       </c>
       <c r="B83" t="n">
-        <v>60.32600402832031</v>
+        <v>60.32601547241211</v>
       </c>
       <c r="C83" t="n">
         <v>65.55000305175781</v>
@@ -1939,7 +1939,7 @@
         <v>42035</v>
       </c>
       <c r="B84" t="n">
-        <v>58.64876174926758</v>
+        <v>58.64875793457031</v>
       </c>
       <c r="C84" t="n">
         <v>63.72750091552734</v>
@@ -1973,7 +1973,7 @@
         <v>42094</v>
       </c>
       <c r="B86" t="n">
-        <v>60.30658721923828</v>
+        <v>60.30658340454102</v>
       </c>
       <c r="C86" t="n">
         <v>65.41000366210938</v>
@@ -1990,7 +1990,7 @@
         <v>42124</v>
       </c>
       <c r="B87" t="n">
-        <v>60.89664840698242</v>
+        <v>60.89666748046875</v>
       </c>
       <c r="C87" t="n">
         <v>66.05000305175781</v>
@@ -2007,7 +2007,7 @@
         <v>42155</v>
       </c>
       <c r="B88" t="n">
-        <v>63.43225479125977</v>
+        <v>63.43226623535156</v>
       </c>
       <c r="C88" t="n">
         <v>68.68000030517578</v>
@@ -2024,7 +2024,7 @@
         <v>42185</v>
       </c>
       <c r="B89" t="n">
-        <v>62.01919174194336</v>
+        <v>62.01917266845703</v>
       </c>
       <c r="C89" t="n">
         <v>67.15000152587891</v>
@@ -2041,7 +2041,7 @@
         <v>42216</v>
       </c>
       <c r="B90" t="n">
-        <v>69.58338165283203</v>
+        <v>69.5833740234375</v>
       </c>
       <c r="C90" t="n">
         <v>75.33999633789062</v>
@@ -2058,7 +2058,7 @@
         <v>42247</v>
       </c>
       <c r="B91" t="n">
-        <v>65.95998382568359</v>
+        <v>65.95996856689453</v>
       </c>
       <c r="C91" t="n">
         <v>71.30000305175781</v>
@@ -2075,7 +2075,7 @@
         <v>42277</v>
       </c>
       <c r="B92" t="n">
-        <v>64.44281005859375</v>
+        <v>64.44282531738281</v>
       </c>
       <c r="C92" t="n">
         <v>69.66000366210938</v>
@@ -2092,7 +2092,7 @@
         <v>42308</v>
       </c>
       <c r="B93" t="n">
-        <v>71.7696533203125</v>
+        <v>71.76964569091797</v>
       </c>
       <c r="C93" t="n">
         <v>77.58000183105469</v>
@@ -2109,7 +2109,7 @@
         <v>42338</v>
       </c>
       <c r="B94" t="n">
-        <v>73.22391510009766</v>
+        <v>73.22392272949219</v>
       </c>
       <c r="C94" t="n">
         <v>79.01000213623047</v>
@@ -2143,7 +2143,7 @@
         <v>42400</v>
       </c>
       <c r="B96" t="n">
-        <v>69.03492736816406</v>
+        <v>69.034912109375</v>
       </c>
       <c r="C96" t="n">
         <v>74.48999786376953</v>
@@ -2160,7 +2160,7 @@
         <v>42429</v>
       </c>
       <c r="B97" t="n">
-        <v>67.22105407714844</v>
+        <v>67.2210693359375</v>
       </c>
       <c r="C97" t="n">
         <v>72.38999938964844</v>
@@ -2177,7 +2177,7 @@
         <v>42460</v>
       </c>
       <c r="B98" t="n">
-        <v>71.01902770996094</v>
+        <v>71.01903533935547</v>
       </c>
       <c r="C98" t="n">
         <v>76.48000335693359</v>
@@ -2194,7 +2194,7 @@
         <v>42490</v>
       </c>
       <c r="B99" t="n">
-        <v>71.72473907470703</v>
+        <v>71.72474670410156</v>
       </c>
       <c r="C99" t="n">
         <v>77.23999786376953</v>
@@ -2211,7 +2211,7 @@
         <v>42521</v>
       </c>
       <c r="B100" t="n">
-        <v>73.43314361572266</v>
+        <v>73.43316650390625</v>
       </c>
       <c r="C100" t="n">
         <v>78.94000244140625</v>
@@ -2228,7 +2228,7 @@
         <v>42551</v>
       </c>
       <c r="B101" t="n">
-        <v>68.99591827392578</v>
+        <v>68.99589538574219</v>
       </c>
       <c r="C101" t="n">
         <v>74.16999816894531</v>
@@ -2245,7 +2245,7 @@
         <v>42582</v>
       </c>
       <c r="B102" t="n">
-        <v>72.60527038574219</v>
+        <v>72.60526275634766</v>
       </c>
       <c r="C102" t="n">
         <v>78.05000305175781</v>
@@ -2262,7 +2262,7 @@
         <v>42613</v>
       </c>
       <c r="B103" t="n">
-        <v>75.38706970214844</v>
+        <v>75.38704681396484</v>
       </c>
       <c r="C103" t="n">
         <v>80.90000152587891</v>
@@ -2279,7 +2279,7 @@
         <v>42643</v>
       </c>
       <c r="B104" t="n">
-        <v>77.06438446044922</v>
+        <v>77.06439971923828</v>
       </c>
       <c r="C104" t="n">
         <v>82.69999694824219</v>
@@ -2296,7 +2296,7 @@
         <v>42674</v>
       </c>
       <c r="B105" t="n">
-        <v>76.8873291015625</v>
+        <v>76.88732147216797</v>
       </c>
       <c r="C105" t="n">
         <v>82.51000213623047</v>
@@ -2330,7 +2330,7 @@
         <v>42735</v>
       </c>
       <c r="B107" t="n">
-        <v>72.85630798339844</v>
+        <v>72.85631561279297</v>
       </c>
       <c r="C107" t="n">
         <v>78.01999664306641</v>
@@ -2347,7 +2347,7 @@
         <v>42766</v>
       </c>
       <c r="B108" t="n">
-        <v>77.23590087890625</v>
+        <v>77.23590850830078</v>
       </c>
       <c r="C108" t="n">
         <v>82.70999908447266</v>
@@ -2364,7 +2364,7 @@
         <v>42794</v>
       </c>
       <c r="B109" t="n">
-        <v>82.27605438232422</v>
+        <v>82.27608489990234</v>
       </c>
       <c r="C109" t="n">
         <v>87.94000244140625</v>
@@ -2381,7 +2381,7 @@
         <v>42825</v>
       </c>
       <c r="B110" t="n">
-        <v>83.14617156982422</v>
+        <v>83.14617919921875</v>
       </c>
       <c r="C110" t="n">
         <v>88.87000274658203</v>
@@ -2398,7 +2398,7 @@
         <v>42855</v>
       </c>
       <c r="B111" t="n">
-        <v>85.34483337402344</v>
+        <v>85.34481811523438</v>
       </c>
       <c r="C111" t="n">
         <v>91.22000122070312</v>
@@ -2415,7 +2415,7 @@
         <v>42886</v>
       </c>
       <c r="B112" t="n">
-        <v>89.25466156005859</v>
+        <v>89.254638671875</v>
       </c>
       <c r="C112" t="n">
         <v>95.23000335693359</v>
@@ -2432,7 +2432,7 @@
         <v>42916</v>
       </c>
       <c r="B113" t="n">
-        <v>87.89562225341797</v>
+        <v>87.89560699462891</v>
       </c>
       <c r="C113" t="n">
         <v>93.77999877929688</v>
@@ -2466,7 +2466,7 @@
         <v>42978</v>
       </c>
       <c r="B115" t="n">
-        <v>97.18070983886719</v>
+        <v>97.18071746826172</v>
       </c>
       <c r="C115" t="n">
         <v>103.5199966430664</v>
@@ -2483,7 +2483,7 @@
         <v>43008</v>
       </c>
       <c r="B116" t="n">
-        <v>98.79539489746094</v>
+        <v>98.79537200927734</v>
       </c>
       <c r="C116" t="n">
         <v>105.2399978637695</v>
@@ -2500,7 +2500,7 @@
         <v>43039</v>
       </c>
       <c r="B117" t="n">
-        <v>103.2451324462891</v>
+        <v>103.2451248168945</v>
       </c>
       <c r="C117" t="n">
         <v>109.9800033569336</v>
@@ -2517,7 +2517,7 @@
         <v>43069</v>
       </c>
       <c r="B118" t="n">
-        <v>105.882568359375</v>
+        <v>105.8825759887695</v>
       </c>
       <c r="C118" t="n">
         <v>112.5899963378906</v>
@@ -2534,7 +2534,7 @@
         <v>43100</v>
       </c>
       <c r="B119" t="n">
-        <v>107.2273864746094</v>
+        <v>107.2273559570312</v>
       </c>
       <c r="C119" t="n">
         <v>114.0199966430664</v>
@@ -2551,7 +2551,7 @@
         <v>43131</v>
       </c>
       <c r="B120" t="n">
-        <v>116.8291397094727</v>
+        <v>116.8291320800781</v>
       </c>
       <c r="C120" t="n">
         <v>124.2300033569336</v>
@@ -2568,7 +2568,7 @@
         <v>43159</v>
       </c>
       <c r="B121" t="n">
-        <v>115.8172836303711</v>
+        <v>115.817268371582</v>
       </c>
       <c r="C121" t="n">
         <v>122.9400024414062</v>
@@ -2585,7 +2585,7 @@
         <v>43190</v>
       </c>
       <c r="B122" t="n">
-        <v>112.6896209716797</v>
+        <v>112.6896057128906</v>
       </c>
       <c r="C122" t="n">
         <v>119.620002746582</v>
@@ -2602,7 +2602,7 @@
         <v>43220</v>
       </c>
       <c r="B123" t="n">
-        <v>119.5289840698242</v>
+        <v>119.5289764404297</v>
       </c>
       <c r="C123" t="n">
         <v>126.879997253418</v>
@@ -2619,7 +2619,7 @@
         <v>43251</v>
       </c>
       <c r="B124" t="n">
-        <v>123.3443908691406</v>
+        <v>123.3443984985352</v>
       </c>
       <c r="C124" t="n">
         <v>130.7200012207031</v>
@@ -2636,7 +2636,7 @@
         <v>43281</v>
       </c>
       <c r="B125" t="n">
-        <v>124.9768142700195</v>
+        <v>124.9767761230469</v>
       </c>
       <c r="C125" t="n">
         <v>132.4499969482422</v>
@@ -2653,7 +2653,7 @@
         <v>43312</v>
       </c>
       <c r="B126" t="n">
-        <v>129.0247802734375</v>
+        <v>129.0247497558594</v>
       </c>
       <c r="C126" t="n">
         <v>136.7400054931641</v>
@@ -2687,7 +2687,7 @@
         <v>43373</v>
       </c>
       <c r="B128" t="n">
-        <v>141.8343811035156</v>
+        <v>141.8343658447266</v>
       </c>
       <c r="C128" t="n">
         <v>150.0899963378906</v>
@@ -2704,7 +2704,7 @@
         <v>43404</v>
       </c>
       <c r="B129" t="n">
-        <v>130.2675933837891</v>
+        <v>130.2676391601562</v>
       </c>
       <c r="C129" t="n">
         <v>137.8500061035156</v>
@@ -2721,7 +2721,7 @@
         <v>43434</v>
       </c>
       <c r="B130" t="n">
-        <v>134.15576171875</v>
+        <v>134.1557769775391</v>
       </c>
       <c r="C130" t="n">
         <v>141.7100067138672</v>
@@ -2738,7 +2738,7 @@
         <v>43465</v>
       </c>
       <c r="B131" t="n">
-        <v>124.9065628051758</v>
+        <v>124.9066467285156</v>
       </c>
       <c r="C131" t="n">
         <v>131.9400024414062</v>
@@ -2772,7 +2772,7 @@
         <v>43524</v>
       </c>
       <c r="B133" t="n">
-        <v>140.4687652587891</v>
+        <v>140.4687957763672</v>
       </c>
       <c r="C133" t="n">
         <v>148.1199951171875</v>
@@ -2789,7 +2789,7 @@
         <v>43555</v>
       </c>
       <c r="B134" t="n">
-        <v>148.1219482421875</v>
+        <v>148.1219329833984</v>
       </c>
       <c r="C134" t="n">
         <v>156.1900024414062</v>
@@ -2823,7 +2823,7 @@
         <v>43616</v>
       </c>
       <c r="B136" t="n">
-        <v>153.231689453125</v>
+        <v>153.2317504882812</v>
       </c>
       <c r="C136" t="n">
         <v>161.3300018310547</v>
@@ -2857,7 +2857,7 @@
         <v>43677</v>
       </c>
       <c r="B138" t="n">
-        <v>169.0649566650391</v>
+        <v>169.0649719238281</v>
       </c>
       <c r="C138" t="n">
         <v>178</v>
@@ -2874,7 +2874,7 @@
         <v>43708</v>
       </c>
       <c r="B139" t="n">
-        <v>171.9912567138672</v>
+        <v>171.9912414550781</v>
       </c>
       <c r="C139" t="n">
         <v>180.8200073242188</v>
@@ -2891,7 +2891,7 @@
         <v>43738</v>
       </c>
       <c r="B140" t="n">
-        <v>163.6113433837891</v>
+        <v>163.6113586425781</v>
       </c>
       <c r="C140" t="n">
         <v>172.0099945068359</v>
@@ -2908,7 +2908,7 @@
         <v>43769</v>
       </c>
       <c r="B141" t="n">
-        <v>170.1269073486328</v>
+        <v>170.1269683837891</v>
       </c>
       <c r="C141" t="n">
         <v>178.8600006103516</v>
@@ -2942,7 +2942,7 @@
         <v>43830</v>
       </c>
       <c r="B143" t="n">
-        <v>179.0248565673828</v>
+        <v>179.0248718261719</v>
       </c>
       <c r="C143" t="n">
         <v>187.8999938964844</v>
@@ -2959,7 +2959,7 @@
         <v>43861</v>
       </c>
       <c r="B144" t="n">
-        <v>189.5720062255859</v>
+        <v>189.572021484375</v>
       </c>
       <c r="C144" t="n">
         <v>198.9700012207031</v>
@@ -2976,7 +2976,7 @@
         <v>43890</v>
       </c>
       <c r="B145" t="n">
-        <v>173.4257354736328</v>
+        <v>173.4256439208984</v>
       </c>
       <c r="C145" t="n">
         <v>181.7599945068359</v>
@@ -2993,7 +2993,7 @@
         <v>43921</v>
       </c>
       <c r="B146" t="n">
-        <v>153.7321319580078</v>
+        <v>153.7320861816406</v>
       </c>
       <c r="C146" t="n">
         <v>161.1199951171875</v>
@@ -3010,7 +3010,7 @@
         <v>43951</v>
       </c>
       <c r="B147" t="n">
-        <v>170.5251007080078</v>
+        <v>170.5250701904297</v>
       </c>
       <c r="C147" t="n">
         <v>178.7200012207031</v>
@@ -3027,7 +3027,7 @@
         <v>43982</v>
       </c>
       <c r="B148" t="n">
-        <v>186.5995635986328</v>
+        <v>186.5995178222656</v>
       </c>
       <c r="C148" t="n">
         <v>195.2400054931641</v>
@@ -3044,7 +3044,7 @@
         <v>44012</v>
       </c>
       <c r="B149" t="n">
-        <v>184.6211395263672</v>
+        <v>184.6211242675781</v>
       </c>
       <c r="C149" t="n">
         <v>193.1699981689453</v>
@@ -3078,7 +3078,7 @@
         <v>44074</v>
       </c>
       <c r="B151" t="n">
-        <v>202.9145202636719</v>
+        <v>202.9145355224609</v>
       </c>
       <c r="C151" t="n">
         <v>211.9900054931641</v>
@@ -3095,7 +3095,7 @@
         <v>44104</v>
       </c>
       <c r="B152" t="n">
-        <v>191.4091033935547</v>
+        <v>191.4091339111328</v>
       </c>
       <c r="C152" t="n">
         <v>199.9700012207031</v>
@@ -3112,7 +3112,7 @@
         <v>44135</v>
       </c>
       <c r="B153" t="n">
-        <v>173.9308319091797</v>
+        <v>173.9308624267578</v>
       </c>
       <c r="C153" t="n">
         <v>181.7100067138672</v>
@@ -3163,7 +3163,7 @@
         <v>44227</v>
       </c>
       <c r="B156" t="n">
-        <v>185.2555236816406</v>
+        <v>185.2555389404297</v>
       </c>
       <c r="C156" t="n">
         <v>193.25</v>
@@ -3197,7 +3197,7 @@
         <v>44286</v>
       </c>
       <c r="B158" t="n">
-        <v>203.2860870361328</v>
+        <v>203.2861022949219</v>
       </c>
       <c r="C158" t="n">
         <v>211.7299957275391</v>
@@ -3214,7 +3214,7 @@
         <v>44316</v>
       </c>
       <c r="B159" t="n">
-        <v>224.2455444335938</v>
+        <v>224.2455291748047</v>
       </c>
       <c r="C159" t="n">
         <v>233.5599975585938</v>
@@ -3231,7 +3231,7 @@
         <v>44347</v>
       </c>
       <c r="B160" t="n">
-        <v>218.5522003173828</v>
+        <v>218.5521850585938</v>
       </c>
       <c r="C160" t="n">
         <v>227.3000030517578</v>
@@ -3248,7 +3248,7 @@
         <v>44377</v>
       </c>
       <c r="B161" t="n">
-        <v>224.8212890625</v>
+        <v>224.8212280273438</v>
       </c>
       <c r="C161" t="n">
         <v>233.8200073242188</v>
@@ -3265,7 +3265,7 @@
         <v>44408</v>
       </c>
       <c r="B162" t="n">
-        <v>236.9074859619141</v>
+        <v>236.9075164794922</v>
       </c>
       <c r="C162" t="n">
         <v>246.3899993896484</v>
@@ -3282,7 +3282,7 @@
         <v>44439</v>
       </c>
       <c r="B163" t="n">
-        <v>220.5832061767578</v>
+        <v>220.5832366943359</v>
       </c>
       <c r="C163" t="n">
         <v>229.1000061035156</v>
@@ -3299,7 +3299,7 @@
         <v>44469</v>
       </c>
       <c r="B164" t="n">
-        <v>214.4692687988281</v>
+        <v>214.46923828125</v>
       </c>
       <c r="C164" t="n">
         <v>222.75</v>
@@ -3333,7 +3333,7 @@
         <v>44530</v>
       </c>
       <c r="B166" t="n">
-        <v>186.8950500488281</v>
+        <v>186.8950653076172</v>
       </c>
       <c r="C166" t="n">
         <v>193.7700042724609</v>
@@ -3350,7 +3350,7 @@
         <v>44561</v>
       </c>
       <c r="B167" t="n">
-        <v>209.0211029052734</v>
+        <v>209.0211181640625</v>
       </c>
       <c r="C167" t="n">
         <v>216.7100067138672</v>
@@ -3367,7 +3367,7 @@
         <v>44592</v>
       </c>
       <c r="B168" t="n">
-        <v>218.1454925537109</v>
+        <v>218.1454772949219</v>
       </c>
       <c r="C168" t="n">
         <v>226.1699981689453</v>
@@ -3401,7 +3401,7 @@
         <v>44651</v>
       </c>
       <c r="B170" t="n">
-        <v>214.2495880126953</v>
+        <v>214.2496337890625</v>
       </c>
       <c r="C170" t="n">
         <v>221.7700042724609</v>
@@ -3418,7 +3418,7 @@
         <v>44681</v>
       </c>
       <c r="B171" t="n">
-        <v>205.9026184082031</v>
+        <v>205.9026031494141</v>
       </c>
       <c r="C171" t="n">
         <v>213.1300048828125</v>
@@ -3452,7 +3452,7 @@
         <v>44742</v>
       </c>
       <c r="B173" t="n">
-        <v>190.5765838623047</v>
+        <v>190.5766143798828</v>
       </c>
       <c r="C173" t="n">
         <v>196.8899993896484</v>
@@ -3469,7 +3469,7 @@
         <v>44773</v>
       </c>
       <c r="B174" t="n">
-        <v>205.3085784912109</v>
+        <v>205.3085632324219</v>
       </c>
       <c r="C174" t="n">
         <v>212.1100006103516</v>
@@ -3486,7 +3486,7 @@
         <v>44804</v>
       </c>
       <c r="B175" t="n">
-        <v>192.6788940429688</v>
+        <v>192.6788787841797</v>
       </c>
       <c r="C175" t="n">
         <v>198.7100067138672</v>
@@ -3503,7 +3503,7 @@
         <v>44834</v>
       </c>
       <c r="B176" t="n">
-        <v>172.258056640625</v>
+        <v>172.2580871582031</v>
       </c>
       <c r="C176" t="n">
         <v>177.6499938964844</v>
@@ -3520,7 +3520,7 @@
         <v>44865</v>
       </c>
       <c r="B177" t="n">
-        <v>200.8724670410156</v>
+        <v>200.8724212646484</v>
       </c>
       <c r="C177" t="n">
         <v>207.1600036621094</v>
@@ -3537,7 +3537,7 @@
         <v>44895</v>
       </c>
       <c r="B178" t="n">
-        <v>210.8840637207031</v>
+        <v>210.8840789794922</v>
       </c>
       <c r="C178" t="n">
         <v>217</v>
@@ -3554,7 +3554,7 @@
         <v>44926</v>
       </c>
       <c r="B179" t="n">
-        <v>201.9045257568359</v>
+        <v>201.9044952392578</v>
       </c>
       <c r="C179" t="n">
         <v>207.7599945068359</v>
@@ -3571,7 +3571,7 @@
         <v>44957</v>
       </c>
       <c r="B180" t="n">
-        <v>223.7217864990234</v>
+        <v>223.7217559814453</v>
       </c>
       <c r="C180" t="n">
         <v>230.2100067138672</v>
@@ -3588,7 +3588,7 @@
         <v>44985</v>
       </c>
       <c r="B181" t="n">
-        <v>214.1598358154297</v>
+        <v>214.1598968505859</v>
       </c>
       <c r="C181" t="n">
         <v>219.9400024414062</v>
@@ -3605,7 +3605,7 @@
         <v>45016</v>
       </c>
       <c r="B182" t="n">
-        <v>219.5348052978516</v>
+        <v>219.5347900390625</v>
       </c>
       <c r="C182" t="n">
         <v>225.4600067138672</v>
@@ -3622,7 +3622,7 @@
         <v>45046</v>
       </c>
       <c r="B183" t="n">
-        <v>226.6137390136719</v>
+        <v>226.6137542724609</v>
       </c>
       <c r="C183" t="n">
         <v>232.7299957275391</v>
@@ -3639,7 +3639,7 @@
         <v>45077</v>
       </c>
       <c r="B184" t="n">
-        <v>215.6407775878906</v>
+        <v>215.6408081054688</v>
       </c>
       <c r="C184" t="n">
         <v>221.0299987792969</v>
@@ -3673,7 +3673,7 @@
         <v>45138</v>
       </c>
       <c r="B186" t="n">
-        <v>231.9336242675781</v>
+        <v>231.93359375</v>
       </c>
       <c r="C186" t="n">
         <v>237.7299957275391</v>
@@ -3690,7 +3690,7 @@
         <v>45169</v>
       </c>
       <c r="B187" t="n">
-        <v>240.1405181884766</v>
+        <v>240.1405029296875</v>
       </c>
       <c r="C187" t="n">
         <v>245.6799926757812</v>
@@ -3707,7 +3707,7 @@
         <v>45199</v>
       </c>
       <c r="B188" t="n">
-        <v>224.8238372802734</v>
+        <v>224.8238067626953</v>
       </c>
       <c r="C188" t="n">
         <v>230.0099945068359</v>
@@ -3724,7 +3724,7 @@
         <v>45230</v>
       </c>
       <c r="B189" t="n">
-        <v>229.7990570068359</v>
+        <v>229.7990417480469</v>
       </c>
       <c r="C189" t="n">
         <v>235.1000061035156</v>
@@ -3758,7 +3758,7 @@
         <v>45291</v>
       </c>
       <c r="B191" t="n">
-        <v>255.0215454101562</v>
+        <v>255.0215148925781</v>
       </c>
       <c r="C191" t="n">
         <v>260.3500061035156</v>
@@ -3775,7 +3775,7 @@
         <v>45322</v>
       </c>
       <c r="B192" t="n">
-        <v>267.6673278808594</v>
+        <v>267.6672668457031</v>
       </c>
       <c r="C192" t="n">
         <v>273.260009765625</v>
@@ -3826,7 +3826,7 @@
         <v>45412</v>
       </c>
       <c r="B195" t="n">
-        <v>263.6030578613281</v>
+        <v>263.60302734375</v>
       </c>
       <c r="C195" t="n">
         <v>268.6099853515625</v>
@@ -3843,7 +3843,7 @@
         <v>45443</v>
       </c>
       <c r="B196" t="n">
-        <v>267.8761596679688</v>
+        <v>267.8761291503906</v>
       </c>
       <c r="C196" t="n">
         <v>272.4599914550781</v>
@@ -3860,7 +3860,7 @@
         <v>45473</v>
       </c>
       <c r="B197" t="n">
-        <v>258.05419921875</v>
+        <v>258.0542297363281</v>
       </c>
       <c r="C197" t="n">
         <v>262.4700012207031</v>
@@ -3877,7 +3877,7 @@
         <v>45504</v>
       </c>
       <c r="B198" t="n">
-        <v>261.200439453125</v>
+        <v>261.2004089355469</v>
       </c>
       <c r="C198" t="n">
         <v>265.6700134277344</v>
@@ -3911,7 +3911,7 @@
         <v>45565</v>
       </c>
       <c r="B200" t="n">
-        <v>270.8663635253906</v>
+        <v>270.8663330078125</v>
       </c>
       <c r="C200" t="n">
         <v>274.9500122070312</v>
@@ -3945,7 +3945,7 @@
         <v>45626</v>
       </c>
       <c r="B202" t="n">
-        <v>310.9904479980469</v>
+        <v>310.9903869628906</v>
       </c>
       <c r="C202" t="n">
         <v>315.0799865722656</v>
@@ -3996,7 +3996,7 @@
         <v>45716</v>
       </c>
       <c r="B205" t="n">
-        <v>358.6046142578125</v>
+        <v>358.6046447753906</v>
       </c>
       <c r="C205" t="n">
         <v>362.7099914550781</v>
@@ -4013,7 +4013,7 @@
         <v>45747</v>
       </c>
       <c r="B206" t="n">
-        <v>346.4932556152344</v>
+        <v>346.4932861328125</v>
       </c>
       <c r="C206" t="n">
         <v>350.4599914550781</v>
@@ -4030,7 +4030,7 @@
         <v>45777</v>
       </c>
       <c r="B207" t="n">
-        <v>341.5893859863281</v>
+        <v>341.5894165039062</v>
       </c>
       <c r="C207" t="n">
         <v>345.5</v>
@@ -4047,7 +4047,7 @@
         <v>45808</v>
       </c>
       <c r="B208" t="n">
-        <v>361.6561889648438</v>
+        <v>361.6561279296875</v>
       </c>
       <c r="C208" t="n">
         <v>365.1900024414062</v>
@@ -4081,7 +4081,7 @@
         <v>45869</v>
       </c>
       <c r="B210" t="n">
-        <v>342.1269836425781</v>
+        <v>342.1270141601562</v>
       </c>
       <c r="C210" t="n">
         <v>345.4700012207031</v>
@@ -4115,7 +4115,7 @@
         <v>45930</v>
       </c>
       <c r="B212" t="n">
-        <v>338.6714782714844</v>
+        <v>338.6714477539062</v>
       </c>
       <c r="C212" t="n">
         <v>341.3800048828125</v>
@@ -4132,7 +4132,7 @@
         <v>45961</v>
       </c>
       <c r="B213" t="n">
-        <v>338.0364990234375</v>
+        <v>338.0365295410156</v>
       </c>
       <c r="C213" t="n">
         <v>340.739990234375</v>
@@ -4200,7 +4200,7 @@
         <v>46081</v>
       </c>
       <c r="B217" t="n">
-        <v>318.8852844238281</v>
+        <v>318.8853149414062</v>
       </c>
       <c r="C217" t="n">
         <v>320.1400146484375</v>
@@ -4234,7 +4234,7 @@
         <v>46142</v>
       </c>
       <c r="B219" t="n">
-        <v>328.5472717285156</v>
+        <v>328.5472412109375</v>
       </c>
       <c r="C219" t="n">
         <v>329.8399963378906</v>
